--- a/光伏配储项目/电价数据/2026/炭步站.xlsx
+++ b/光伏配储项目/电价数据/2026/炭步站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50848</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7423999999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57162</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5800599999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49451</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43733</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45411</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42047</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09423000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08645</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11249</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03557</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07854999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09176000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09461</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06403</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08982999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03714</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.03068</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14196</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.21976</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21885</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21103</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01193</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.22186</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11869</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24292</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24028</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25808</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5236000000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48485</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.71772</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.60138</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42719</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42006</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45132</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.60412</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79034</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.64152</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6051299999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73391</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.8693099999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6613300000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58617</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48752</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.43532</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6231599999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47019</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.68841</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.16038</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.6706599999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.7380599999999999</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.7083200000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5029399999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5176499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41884</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49521</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.57075</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.55472</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15379</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06367</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74288</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9539099999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.6710700000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.46856</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.15477</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28683</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22684</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.23677</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41369</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49385</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.59777</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6678200000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6570900000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71361</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7546799999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.5688799999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48309</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43391</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50797</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36688</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20263</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22327</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.20427</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16953</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5559400000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17005</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.45611</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5147999999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59853</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6049099999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45218</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43291</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45226</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39617</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40868</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.40506</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36392</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43349</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44518</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14802</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16909</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2643</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5666599999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26225</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.06919</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.08965999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.19583</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20753</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6513</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07285999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.17489</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29349</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.17151</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48593</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.48297</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.52335</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29306</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29936</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04786</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.06261</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.06498000000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.05891</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06297999999999999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02672</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02725</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01724</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02533</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02609</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.01426</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03671</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.01836</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03625</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03918</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03845000000000001</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04514</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.01912</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.02485</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21933</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.06555</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0745</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05932</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00396</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15182</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09173999999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40073</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41018</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35138</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6554500000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.01804</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03502</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12033</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.006480000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.01279</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.01051</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03845000000000001</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02547</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.02755</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04998</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33562</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31712</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9138999999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8620599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29571</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88663</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6314299999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18622</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86833</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54427</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.32997</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03231</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5299199999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79026</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53203</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77224</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77696</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87348</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49247</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.399</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44915</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2061</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62097</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5380900000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41501</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43411</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5877599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59649</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60342</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6952999999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58227</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45209</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8848200000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6354500000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84411</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8236100000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44213</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26306</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29583</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45416</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35381</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91912</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5023299999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28874</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16403</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26203</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19344</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.60045</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89134</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35936</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16628</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79222</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6690199999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45405</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50198</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44105</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41607</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50375</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45308</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42449</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49582</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54203</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11569</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27235</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26965</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5714900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46458</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32463</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42441</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22041</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14211</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15048</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14173</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13484</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14072</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24176</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25085</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25337</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13228</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09118999999999999</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10523</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11588</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1323</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1366</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44538</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34937</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5414099999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47054</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24252</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39246</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36088</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25161</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25138</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08826000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22587</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29703</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6890299999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21911</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29144</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44312</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.43512</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.43958</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38948</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.49172</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35003</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41185</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77787</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45988</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28668</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21434</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2761</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43857</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46208</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.68712</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.64262</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6550900000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5397000000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8832100000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49493</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.87005</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.51358</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5164</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36071</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52955</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48683</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40364</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41467</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45213</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56662</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50528</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49024</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40212</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.62597</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.18668</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49487</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44042</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5490499999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.28597</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.59135</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.74074</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.76276</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.04276</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.13076</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81377</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58636</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52697</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8384199999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76888</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233200000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6716799999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44064</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47269</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48419</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47892</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47131</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41839</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55443</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42907</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38114</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18703</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10747</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18283</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.368</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27048</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22929</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22838</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24408</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14355</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24721</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04385</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16685</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18562</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29922</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23307</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23664</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3514</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31345</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22707</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01825</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15766</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04383</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04196</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04849000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03012</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01502</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01317</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03412</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21531</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48659</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38233</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.42246</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40665</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.99383</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9731000000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47901</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.60004</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.47478</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48897</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.56692</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41498</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.40274</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38315</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46846</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.00407</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.07665</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.94455</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.98798</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.20965</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18832</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.19133</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00735</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08513</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25393</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3973</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32397</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49529</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52122</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48201</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43876</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14047</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49188</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25488</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47205</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39334</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.57412</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23824</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36878</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47838</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49442</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57182</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56221</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.62607</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49541</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.52225</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47054</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.61291</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.73693</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7010299999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53326</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.53335</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37295</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3786600000000001</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14244</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13357</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20288</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15487</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00761</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25815</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14675</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05739</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04257</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06656000000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18224</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07169</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.22015</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15912</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19181</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36387</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.44085</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48552</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38788</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06941</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.57653</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.52236</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46629</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41546</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.02004</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01667</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.02638</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03882</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00666</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04297</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.009789999999999998</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1555</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04035</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.18797</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44095</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41403</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37025</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48734</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39942</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39212</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38289</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18601</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15538</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12279</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.22933</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04702000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04956</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04595</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04564</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10293</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02957</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.08033</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13338</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24364</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16902</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21392</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1539</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26442</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40589</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39345</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39805</v>
       </c>
     </row>
   </sheetData>
